--- a/joborderpersonnels.xlsx
+++ b/joborderpersonnels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\DTR-Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52D89DA-B3A9-4CB6-961B-CC38BAD287D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B789C2-B3F6-4DA9-9F4F-9369D0F38179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6831A95B-8140-4EBC-B9A1-5EB659DA3437}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6831A95B-8140-4EBC-B9A1-5EB659DA3437}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="130">
   <si>
     <t>ADAYA, JAYNEL</t>
   </si>
@@ -56,24 +56,12 @@
     <t>JobOrderName</t>
   </si>
   <si>
-    <t>PONTE, JOSEF</t>
-  </si>
-  <si>
     <t>NurseName</t>
   </si>
   <si>
     <t>TANSIONGCO, JOHN</t>
   </si>
   <si>
-    <t>JURINARIO, NICOLE</t>
-  </si>
-  <si>
-    <t>OLLOSA, JASON</t>
-  </si>
-  <si>
-    <t>TestNames</t>
-  </si>
-  <si>
     <t>ANAPE, JOHN</t>
   </si>
   <si>
@@ -98,24 +86,9 @@
     <t>ESPADA, JONEL</t>
   </si>
   <si>
-    <t>FALALIMPA, ZYRENE</t>
-  </si>
-  <si>
-    <t>GALISTE, JENETH</t>
-  </si>
-  <si>
     <t>JACOSALEM, MYLYN</t>
   </si>
   <si>
-    <t>JAPITANA, REY</t>
-  </si>
-  <si>
-    <t>LANESTOSA, SHALENE</t>
-  </si>
-  <si>
-    <t>LESONDATO, SWEDEN</t>
-  </si>
-  <si>
     <t>LEUTERIO, MARK</t>
   </si>
   <si>
@@ -137,27 +110,15 @@
     <t>PANES, PAMELA</t>
   </si>
   <si>
-    <t>PASUGIRON, VEVA</t>
-  </si>
-  <si>
-    <t>APITA, ALYZZA</t>
-  </si>
-  <si>
     <t>BALES, JOHN MARLOU</t>
   </si>
   <si>
-    <t>CABUCTOLAH, RODOLFO</t>
-  </si>
-  <si>
     <t>CAMPANI, JESSAVIL</t>
   </si>
   <si>
     <t>DAILAN, MARJON</t>
   </si>
   <si>
-    <t>DENOSTA, CLEARIE</t>
-  </si>
-  <si>
     <t>ESCOBIA, JAYBI</t>
   </si>
   <si>
@@ -185,21 +146,12 @@
     <t>SULATORIO, ANGEL</t>
   </si>
   <si>
-    <t>TANUTAN, GIBB</t>
-  </si>
-  <si>
     <t>TEJADA, MONICA</t>
   </si>
   <si>
-    <t>TONGA, JERRYLYN</t>
-  </si>
-  <si>
     <t>VEGAFRIA, RAVEN</t>
   </si>
   <si>
-    <t>BANATE, RYJEAN</t>
-  </si>
-  <si>
     <t>BATIDUAN, PAUL</t>
   </si>
   <si>
@@ -210,13 +162,277 @@
   </si>
   <si>
     <t>EL JUN GALLARDO</t>
+  </si>
+  <si>
+    <t>ABONADO, SERAFIN</t>
+  </si>
+  <si>
+    <t>AGUDA, MA. JESICA</t>
+  </si>
+  <si>
+    <t>ALAMODIN, MA. LEILA</t>
+  </si>
+  <si>
+    <t>ALILIGAY, ALVIN</t>
+  </si>
+  <si>
+    <t>AMBOY, TREXEL</t>
+  </si>
+  <si>
+    <t>ANDRES, LAINIE</t>
+  </si>
+  <si>
+    <t>ARMADA, JOERENA</t>
+  </si>
+  <si>
+    <t>ASCURA, MATT</t>
+  </si>
+  <si>
+    <t>AURELIO, RONCHES</t>
+  </si>
+  <si>
+    <t>BARADAS, CHERRYL</t>
+  </si>
+  <si>
+    <t>BARROCAMO, EMMY</t>
+  </si>
+  <si>
+    <t>BAS, KEITH</t>
+  </si>
+  <si>
+    <t>BEJEMINO, RACHAEL</t>
+  </si>
+  <si>
+    <t>BROWN, REGINA</t>
+  </si>
+  <si>
+    <t>BURLA, MARY</t>
+  </si>
+  <si>
+    <t>BUSTAMANTE, ED</t>
+  </si>
+  <si>
+    <t>CABARLES, ARLENE</t>
+  </si>
+  <si>
+    <t>CAMBAS, ROLAND</t>
+  </si>
+  <si>
+    <t>CASTILLO, JUVIESANT</t>
+  </si>
+  <si>
+    <t>CATUNAO, KRIS</t>
+  </si>
+  <si>
+    <t>COCJIN, GRACE</t>
+  </si>
+  <si>
+    <t>DACLIS, AILEEN</t>
+  </si>
+  <si>
+    <t>DELATANID, MA. TESSA</t>
+  </si>
+  <si>
+    <t>DEMONTANO, JEISHA</t>
+  </si>
+  <si>
+    <t>ESTILO, STEVEN</t>
+  </si>
+  <si>
+    <t>GUMBAN, SALVE</t>
+  </si>
+  <si>
+    <t>JAMINDANG, GLORIA</t>
+  </si>
+  <si>
+    <t>JUAREZ, JUDY</t>
+  </si>
+  <si>
+    <t>KEW, AILENE</t>
+  </si>
+  <si>
+    <t>LABIANG, ELCY</t>
+  </si>
+  <si>
+    <t>LAPIDEZ, ARRIANE</t>
+  </si>
+  <si>
+    <t>MADERSE, CAROL</t>
+  </si>
+  <si>
+    <t>MADOGINOG, RHYS</t>
+  </si>
+  <si>
+    <t>MAESTRO, LALAINE</t>
+  </si>
+  <si>
+    <t>MALLORCA, LOLITA</t>
+  </si>
+  <si>
+    <t>MALLORCA, ROBERTO</t>
+  </si>
+  <si>
+    <t>MENDOZA, AIMEE</t>
+  </si>
+  <si>
+    <t>MIRASOL, GEM</t>
+  </si>
+  <si>
+    <t>MIRASOL, JETHRO</t>
+  </si>
+  <si>
+    <t>MOLINOS, MARKO</t>
+  </si>
+  <si>
+    <t>MONTEFRIO, FELIE</t>
+  </si>
+  <si>
+    <t>MORENO, JEROME</t>
+  </si>
+  <si>
+    <t>NOVILLA, RICHARD</t>
+  </si>
+  <si>
+    <t>OBAOB, MYRAH</t>
+  </si>
+  <si>
+    <t>OLIVARES, LILIBETH</t>
+  </si>
+  <si>
+    <t>ORTIZ, ANNE</t>
+  </si>
+  <si>
+    <t>PADERNILLA, JANO</t>
+  </si>
+  <si>
+    <t>PALU-AY, JAY</t>
+  </si>
+  <si>
+    <t>PANES, FELAMIE</t>
+  </si>
+  <si>
+    <t>PEDRICO, EDWIN</t>
+  </si>
+  <si>
+    <t>PERASOL, CHARMAINE</t>
+  </si>
+  <si>
+    <t>RABAGO, ROMANA</t>
+  </si>
+  <si>
+    <t>REDANIEL, MA. SALLY</t>
+  </si>
+  <si>
+    <t>SALVACION, YVETTE</t>
+  </si>
+  <si>
+    <t>SANTILLAN, JOSE</t>
+  </si>
+  <si>
+    <t>SANTOME, RAYMOND</t>
+  </si>
+  <si>
+    <t>SINOY, HYACINTH</t>
+  </si>
+  <si>
+    <t>SOBREJUANITE, REDA</t>
+  </si>
+  <si>
+    <t>SOTIAR, EUGENIA</t>
+  </si>
+  <si>
+    <t>STA. CRUZ, JOHN</t>
+  </si>
+  <si>
+    <t>TAN, MARIE</t>
+  </si>
+  <si>
+    <t>TANTIADO, MA. JESSICA</t>
+  </si>
+  <si>
+    <t>TORREMORO, JEAN</t>
+  </si>
+  <si>
+    <t>TRASFIERO, RYAN</t>
+  </si>
+  <si>
+    <t>TUTICA, LELANIE</t>
+  </si>
+  <si>
+    <t>VILLANUEVA, JOHN</t>
+  </si>
+  <si>
+    <t>VILLAROSA, JOSE</t>
+  </si>
+  <si>
+    <t>YOUNIS, ELLAINE</t>
+  </si>
+  <si>
+    <t>MARLENE NIEVA</t>
+  </si>
+  <si>
+    <t>VAN ALLAN ZARRIZ</t>
+  </si>
+  <si>
+    <t>EGUALE, ALBEROSE</t>
+  </si>
+  <si>
+    <t>ALTEA, CHERYLL</t>
+  </si>
+  <si>
+    <t>PACARDO, CARL</t>
+  </si>
+  <si>
+    <t>VILLANUEVA, EDCIR</t>
+  </si>
+  <si>
+    <t>SILA, VIRNALIZA</t>
+  </si>
+  <si>
+    <t>TICAR, YESHA</t>
+  </si>
+  <si>
+    <t>CARO, REGIE</t>
+  </si>
+  <si>
+    <t>SAMONTANES, SHEALTIEL</t>
+  </si>
+  <si>
+    <t>CANTE, DANIEL</t>
+  </si>
+  <si>
+    <t>RONDAEL, THERESA</t>
+  </si>
+  <si>
+    <t>DE LOS REYES, ZEN</t>
+  </si>
+  <si>
+    <t>DENBHI LANGREO</t>
+  </si>
+  <si>
+    <t>LUJAN, JEMIMAH</t>
+  </si>
+  <si>
+    <t>ILISAN, ANDREA</t>
+  </si>
+  <si>
+    <t>Supply</t>
+  </si>
+  <si>
+    <t>JANE NAPAWIT</t>
+  </si>
+  <si>
+    <t>CABUCTOLAN, RODOLFO</t>
+  </si>
+  <si>
+    <t>AGUIRRE, JULIAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +448,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -241,10 +463,36 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -253,9 +501,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1210EA2A-C124-48CE-BE32-5813A5795DF8}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.7109375" customWidth="1"/>
@@ -598,299 +853,556 @@
     <col min="3" max="3" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="B2" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
+      <c r="B3" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="B4" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
+      <c r="B5" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B40" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B42" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>125</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
